--- a/resultados/comparacao_ceilandia/comparativo_CN15_vs_CN12.xlsx
+++ b/resultados/comparacao_ceilandia/comparativo_CN15_vs_CN12.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB6"/>
+  <dimension ref="A1:AB7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -570,14 +570,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Base 60%</t>
+          <t>Rede 20%</t>
         </is>
       </c>
       <c r="C2" t="b">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E2" t="n">
         <v>0.92</v>
@@ -586,64 +586,64 @@
         <v>158</v>
       </c>
       <c r="G2" t="n">
-        <v>5513.100000000002</v>
+        <v>1837.699999999998</v>
       </c>
       <c r="H2" t="n">
-        <v>5992.5</v>
+        <v>1997.5</v>
       </c>
       <c r="I2" t="n">
-        <v>4979.795230630747</v>
+        <v>1872.580583471022</v>
       </c>
       <c r="J2" t="n">
-        <v>2396.141701245928</v>
+        <v>838.8818170539066</v>
       </c>
       <c r="K2" t="n">
-        <v>5526.287686273893</v>
+        <v>2051.896864995007</v>
       </c>
       <c r="L2" t="n">
-        <v>4509.667249722361</v>
+        <v>1837.421201307494</v>
       </c>
       <c r="M2" t="n">
-        <v>470.1279809083865</v>
+        <v>35.15938216352789</v>
       </c>
       <c r="N2" t="n">
-        <v>475.0590390579663</v>
+        <v>56.18147986143121</v>
       </c>
       <c r="O2" t="n">
-        <v>0.88884</v>
+        <v>0.97492</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9065002200922968</v>
+        <v>0.9805476950672646</v>
       </c>
       <c r="Q2" t="n">
-        <v>92.14256948910361</v>
+        <v>98.12268969585362</v>
       </c>
       <c r="R2" t="n">
-        <v>90.5592909118707</v>
+        <v>98.12241019297784</v>
       </c>
       <c r="S2" t="n">
-        <v>36.31113233716419</v>
+        <v>36.31093133716419</v>
       </c>
       <c r="T2" t="n">
-        <v>13.8987258734377</v>
+        <v>13.39570347011929</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>992</v>
       </c>
       <c r="V2" t="n">
-        <v>992</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
         <v>1115</v>
       </c>
       <c r="X2" t="n">
-        <v>446</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>365</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>128</v>
+        <v>1115</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -662,14 +662,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rede 80%</t>
+          <t>Rede 40%</t>
         </is>
       </c>
       <c r="C3" t="b">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E3" t="n">
         <v>0.92</v>
@@ -678,64 +678,64 @@
         <v>158</v>
       </c>
       <c r="G3" t="n">
-        <v>7350.799999999992</v>
+        <v>3675.399999999996</v>
       </c>
       <c r="H3" t="n">
-        <v>7990</v>
+        <v>3995</v>
       </c>
       <c r="I3" t="n">
-        <v>6327.093898995045</v>
+        <v>3767.167117312469</v>
       </c>
       <c r="J3" t="n">
-        <v>3144.252939683531</v>
+        <v>1774.608141939857</v>
       </c>
       <c r="K3" t="n">
-        <v>7065.298560953305</v>
+        <v>4164.226476453889</v>
       </c>
       <c r="L3" t="n">
-        <v>5559.566504489593</v>
+        <v>3622.263316929938</v>
       </c>
       <c r="M3" t="n">
-        <v>767.5273945054511</v>
+        <v>144.9038003825308</v>
       </c>
       <c r="N3" t="n">
-        <v>775.9203140994192</v>
+        <v>231.5649624039139</v>
       </c>
       <c r="O3" t="n">
-        <v>0.85769</v>
+        <v>0.94881</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8802457294994676</v>
+        <v>0.9602039940209267</v>
       </c>
       <c r="Q3" t="n">
-        <v>90.54574474263109</v>
+        <v>96.20700844869924</v>
       </c>
       <c r="R3" t="n">
-        <v>87.86919545121086</v>
+        <v>96.1535075065662</v>
       </c>
       <c r="S3" t="n">
-        <v>36.31113233716419</v>
+        <v>36.31093133716419</v>
       </c>
       <c r="T3" t="n">
-        <v>13.8987258734377</v>
+        <v>13.39570347011929</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>992</v>
       </c>
       <c r="V3" t="n">
-        <v>992</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>1115</v>
       </c>
       <c r="X3" t="n">
-        <v>795</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>69</v>
+        <v>1115</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -754,14 +754,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rede 100%</t>
+          <t>Base 60%</t>
         </is>
       </c>
       <c r="C4" t="b">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="E4" t="n">
         <v>0.92</v>
@@ -770,64 +770,64 @@
         <v>158</v>
       </c>
       <c r="G4" t="n">
-        <v>9188.499999999991</v>
+        <v>5513.100000000002</v>
       </c>
       <c r="H4" t="n">
-        <v>9987.5</v>
+        <v>5992.5</v>
       </c>
       <c r="I4" t="n">
-        <v>7550.217000469897</v>
+        <v>5438.696955042018</v>
       </c>
       <c r="J4" t="n">
-        <v>3863.037654348703</v>
+        <v>2676.666500081693</v>
       </c>
       <c r="K4" t="n">
-        <v>8481.086998321653</v>
+        <v>6061.680305116965</v>
       </c>
       <c r="L4" t="n">
-        <v>6445.457568780764</v>
+        <v>5131.89251661762</v>
       </c>
       <c r="M4" t="n">
-        <v>1104.759431689134</v>
+        <v>306.8044384243982</v>
       </c>
       <c r="N4" t="n">
-        <v>1117.326444491502</v>
+        <v>490.5231316248228</v>
       </c>
       <c r="O4" t="n">
-        <v>0.82897</v>
+        <v>0.9251299999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8560180333688322</v>
+        <v>0.9417020687593421</v>
       </c>
       <c r="Q4" t="n">
-        <v>89.26715644329346</v>
+        <v>94.72835951740372</v>
       </c>
       <c r="R4" t="n">
-        <v>85.36784530007048</v>
+        <v>94.35886130518871</v>
       </c>
       <c r="S4" t="n">
-        <v>36.31113233716419</v>
+        <v>36.31093133716419</v>
       </c>
       <c r="T4" t="n">
-        <v>13.8987258734377</v>
+        <v>13.39570347011929</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>992</v>
       </c>
       <c r="V4" t="n">
-        <v>992</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>1115</v>
       </c>
       <c r="X4" t="n">
-        <v>845</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="Z4" t="n">
-        <v>30</v>
+        <v>987</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -846,14 +846,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rede 120%</t>
+          <t>Rede 80%</t>
         </is>
       </c>
       <c r="C5" t="b">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="E5" t="n">
         <v>0.92</v>
@@ -862,64 +862,64 @@
         <v>158</v>
       </c>
       <c r="G5" t="n">
-        <v>11026.2</v>
+        <v>7350.799999999992</v>
       </c>
       <c r="H5" t="n">
-        <v>11985</v>
+        <v>7990</v>
       </c>
       <c r="I5" t="n">
-        <v>8664.686371278074</v>
+        <v>6975.630781132572</v>
       </c>
       <c r="J5" t="n">
-        <v>4552.161943665034</v>
+        <v>3573.529495006286</v>
       </c>
       <c r="K5" t="n">
-        <v>9787.694737473386</v>
+        <v>7837.699780315913</v>
       </c>
       <c r="L5" t="n">
-        <v>7194.849826996289</v>
+        <v>6462.530972574113</v>
       </c>
       <c r="M5" t="n">
-        <v>1469.836544281784</v>
+        <v>513.0998085584598</v>
       </c>
       <c r="N5" t="n">
-        <v>1487.211861872296</v>
+        <v>820.5425372907404</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8024299999999999</v>
+        <v>0.9026900000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8336048952786652</v>
+        <v>0.9241337040358744</v>
       </c>
       <c r="Q5" t="n">
-        <v>88.23757805866545</v>
+        <v>93.47524992625107</v>
       </c>
       <c r="R5" t="n">
-        <v>83.03647147398159</v>
+        <v>92.64439554418114</v>
       </c>
       <c r="S5" t="n">
-        <v>36.31113233716419</v>
+        <v>36.31093133716419</v>
       </c>
       <c r="T5" t="n">
-        <v>13.8987258734377</v>
+        <v>13.39570347011929</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>992</v>
       </c>
       <c r="V5" t="n">
-        <v>992</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>1115</v>
       </c>
       <c r="X5" t="n">
-        <v>867</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>47</v>
+        <v>907</v>
       </c>
       <c r="Z5" t="n">
-        <v>25</v>
+        <v>208</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -938,14 +938,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rede 160%</t>
+          <t>Rede 100%</t>
         </is>
       </c>
       <c r="C6" t="b">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="E6" t="n">
         <v>0.92</v>
@@ -954,69 +954,161 @@
         <v>158</v>
       </c>
       <c r="G6" t="n">
-        <v>14701.59999999998</v>
+        <v>9188.499999999991</v>
       </c>
       <c r="H6" t="n">
-        <v>15980</v>
+        <v>9987.5</v>
       </c>
       <c r="I6" t="n">
-        <v>10617.7501371555</v>
+        <v>8393.797014255442</v>
       </c>
       <c r="J6" t="n">
-        <v>5842.591231166993</v>
+        <v>4461.828182835128</v>
       </c>
       <c r="K6" t="n">
-        <v>12119.09609952719</v>
+        <v>9505.984380886885</v>
       </c>
       <c r="L6" t="n">
-        <v>8368.833115224692</v>
+        <v>7638.708515903331</v>
       </c>
       <c r="M6" t="n">
-        <v>2248.917021930809</v>
+        <v>755.0884983521112</v>
       </c>
       <c r="N6" t="n">
-        <v>2277.51997155587</v>
+        <v>1207.791251895451</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7549899999999999</v>
+        <v>0.8814100000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7935061022364217</v>
+        <v>0.9074291001494768</v>
       </c>
       <c r="Q6" t="n">
-        <v>86.73245766473595</v>
+        <v>92.40627768861061</v>
       </c>
       <c r="R6" t="n">
-        <v>78.81926968632457</v>
+        <v>91.00420826153264</v>
       </c>
       <c r="S6" t="n">
-        <v>36.31113233716419</v>
+        <v>36.31093133716419</v>
       </c>
       <c r="T6" t="n">
-        <v>13.8987258734377</v>
+        <v>13.39570347011929</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>992</v>
       </c>
       <c r="V6" t="n">
-        <v>992</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>1115</v>
       </c>
       <c r="X6" t="n">
-        <v>909</v>
+        <v>742</v>
       </c>
       <c r="Y6" t="n">
-        <v>12</v>
+        <v>190</v>
       </c>
       <c r="Z6" t="n">
-        <v>18</v>
+        <v>183</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="inlineStr">
+        <is>
+          <t>Snapshot estatico</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CN12</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rede 120%</t>
+        </is>
+      </c>
+      <c r="C7" t="b">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>120</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F7" t="n">
+        <v>158</v>
+      </c>
+      <c r="G7" t="n">
+        <v>11026.2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>11985</v>
+      </c>
+      <c r="I7" t="n">
+        <v>9704.108048577717</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5337.556052983435</v>
+      </c>
+      <c r="K7" t="n">
+        <v>11075.1621946232</v>
+      </c>
+      <c r="L7" t="n">
+        <v>8678.744104391144</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1025.363944186573</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1640.464525385532</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.8612100000000001</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.8915423288490284</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>91.49185990353405</v>
+      </c>
+      <c r="R7" t="n">
+        <v>89.43371261888562</v>
+      </c>
+      <c r="S7" t="n">
+        <v>36.31093133716419</v>
+      </c>
+      <c r="T7" t="n">
+        <v>13.39570347011929</v>
+      </c>
+      <c r="U7" t="n">
+        <v>992</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1115</v>
+      </c>
+      <c r="X7" t="n">
+        <v>907</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>57</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>151</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="inlineStr">
         <is>
           <t>Snapshot estatico</t>
         </is>
@@ -1033,7 +1125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1066,14 +1158,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Base 60%</t>
+          <t>Rede 20%</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8453000000000001</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8639</v>
+        <v>0.9489</v>
       </c>
     </row>
     <row r="3">
@@ -1084,14 +1176,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rede 80%</t>
+          <t>Rede 40%</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.8047</v>
+        <v>0.8907</v>
       </c>
       <c r="D3" t="n">
-        <v>0.828</v>
+        <v>0.9038</v>
       </c>
     </row>
     <row r="4">
@@ -1102,14 +1194,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rede 100%</t>
+          <t>Base 60%</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.7684</v>
+        <v>0.8453000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7959000000000001</v>
+        <v>0.8639</v>
       </c>
     </row>
     <row r="5">
@@ -1120,14 +1212,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rede 120%</t>
+          <t>Rede 80%</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.7356</v>
+        <v>0.8047</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7669</v>
+        <v>0.828</v>
       </c>
     </row>
     <row r="6">
@@ -1138,14 +1230,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rede 160%</t>
+          <t>Rede 100%</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.679</v>
+        <v>0.7684</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7167</v>
+        <v>0.7959000000000001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CN15</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rede 120%</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.7356</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.7669</v>
       </c>
     </row>
   </sheetData>
@@ -1199,14 +1309,14 @@
         <v>495</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
       <c r="D2" t="n">
-        <v>0.35</v>
+        <v>0.0541</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>estimada_conservadora</t>
+          <t>SEGCON_BDGD</t>
         </is>
       </c>
     </row>
@@ -1220,14 +1330,14 @@
         <v>191</v>
       </c>
       <c r="C3" t="n">
-        <v>0.33</v>
+        <v>0.298</v>
       </c>
       <c r="D3" t="n">
-        <v>0.34</v>
+        <v>0.4025</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>estimada_conservadora</t>
+          <t>SEGCON_BDGD</t>
         </is>
       </c>
     </row>
@@ -1241,14 +1351,14 @@
         <v>171</v>
       </c>
       <c r="C4" t="n">
-        <v>0.45</v>
+        <v>0.114</v>
       </c>
       <c r="D4" t="n">
-        <v>0.35</v>
+        <v>0.114</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>estimada_conservadora</t>
+          <t>SEGCON_BDGD</t>
         </is>
       </c>
     </row>
@@ -1262,14 +1372,14 @@
         <v>109</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2999999999999999</v>
+        <v>1.5289</v>
       </c>
       <c r="D5" t="n">
-        <v>0.33</v>
+        <v>0.4638</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>estimada_conservadora</t>
+          <t>SEGCON_BDGD</t>
         </is>
       </c>
     </row>
@@ -1283,14 +1393,14 @@
         <v>25</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7</v>
+        <v>1.5289</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4</v>
+        <v>0.4637999999999999</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>estimada_conservadora</t>
+          <t>SEGCON_BDGD</t>
         </is>
       </c>
     </row>
@@ -1304,14 +1414,14 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4</v>
+        <v>0.6047</v>
       </c>
       <c r="D7" t="n">
-        <v>0.35</v>
+        <v>0.4288</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>estimada_conservadora</t>
+          <t>SEGCON_BDGD</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1496,7 @@
         <v>128.5</v>
       </c>
       <c r="C4" t="n">
-        <v>36.31113233716419</v>
+        <v>36.31093133716419</v>
       </c>
     </row>
     <row r="5">
@@ -1399,7 +1509,7 @@
         <v>16.42</v>
       </c>
       <c r="C5" t="n">
-        <v>13.8987258734377</v>
+        <v>13.39570347011929</v>
       </c>
     </row>
     <row r="6">
@@ -1412,7 +1522,7 @@
         <v>0.3331</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4416129032258065</v>
+        <v>0.4712845766129033</v>
       </c>
     </row>
     <row r="7">
@@ -1425,7 +1535,7 @@
         <v>0.292</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
     </row>
   </sheetData>
